--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Aplicación/duoc/archivos de referencia/Instalaciones.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Aplicación/duoc/archivos de referencia/Instalaciones.xlsx
@@ -487,22 +487,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>317802015</t>
+          <t>773747253</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YV2RT4ZA5RA900081</t>
+          <t>YV2RT4ZA5RA280482</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A900081</t>
+          <t>A280482</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A900081 TRANSPORTES JUAN PEREZ DEMO EIRL</t>
+          <t>A280482 TRANSPORTES JUAN PEREZ DEMO EIRL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -542,22 +542,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>319069052</t>
+          <t>77918675K</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YV2XT4ZA1TA900112</t>
+          <t>YV2XT4ZA1TA276344</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A900112</t>
+          <t>A276344</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A900112 CONSTRUCTORA VALLE CENTRAL DEMO SPA</t>
+          <t>A276344 CONSTRUCTORA VALLE CENTRAL DEMO SPA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+56999000005; +56999000006</t>
+          <t>+56988939057; +56956368156</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -609,22 +609,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9BVRT4ZD6PE900038</t>
+          <t>9BVRT4ZD6PE891576</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>E900038</t>
+          <t>E891576</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>E900038 FORESTAL ARAUCANIA FICTICIA S.A.</t>
+          <t>E891576 FORESTAL ARAUCANIA FICTICIA S.A.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+56999000024; +56999000025; +56999000026</t>
+          <t>+56911363139; +56990241687; +56965985879</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -676,22 +676,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9BVRT4ZC5TA900031</t>
+          <t>9BVRT4ZC5TA599724</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A900031</t>
+          <t>A599724</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A900031 FORESTAL ARAUCANIA FICTICIA S.A.</t>
+          <t>A599724 FORESTAL ARAUCANIA FICTICIA S.A.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+56999000024; +56999000025; +56999000026</t>
+          <t>+56911363139; +56990241687; +56965985879</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -743,22 +743,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>321444752</t>
+          <t>785172752</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YV2XT4ZD6TE900125</t>
+          <t>YV2XT4ZD6TE839290</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E900125</t>
+          <t>E839290</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E900125 LOGISTICA ATACAMA FICTICIA SPA</t>
+          <t>E839290 LOGISTICA ATACAMA FICTICIA SPA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+56999000007; +56999000008</t>
+          <t>+56964304013; +56975863067</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -810,22 +810,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>32104880K</t>
+          <t>784579840</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9BVRB40B5RA900012</t>
+          <t>9BVRB40B5RA593708</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A900012</t>
+          <t>A593708</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A900012 INDUSTRIAS METALICAS DEMO LTDA</t>
+          <t>A593708 INDUSTRIAS METALICAS DEMO LTDA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+56999000031; +56999000032</t>
+          <t>+56978374563; +56921741106</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -877,22 +877,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>317643630</t>
+          <t>772902824</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YV2TE2AB8RA900095</t>
+          <t>YV2TE2AB8RA543380</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A900095</t>
+          <t>A543380</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A900095 CARGA MIXTA AUSTRAL DEMO SPA</t>
+          <t>A543380 CARGA MIXTA AUSTRAL DEMO SPA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+56999000013; +56999000014; +56999000015</t>
+          <t>+56924597160; +56981374654; +56986155157</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>32279098K</t>
+          <t>789555699</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YV2XT4ZA9PA900116</t>
+          <t>YV2XT4ZA9PA653268</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A900116</t>
+          <t>A653268</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A900116 SERVICIOS INDUSTRIALES BIOBIO DEMO SPA</t>
+          <t>A653268 SERVICIOS INDUSTRIALES BIOBIO DEMO SPA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+56999000010; +56999000011</t>
+          <t>+56946248600; +56959279643</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1092,22 +1092,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>32104880K</t>
+          <t>784579840</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9BVRB40B5RA900012</t>
+          <t>9BVRB40B5RA593708</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A900012</t>
+          <t>A593708</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A900012 INDUSTRIAS METALICAS DEMO LTDA</t>
+          <t>A593708 INDUSTRIAS METALICAS DEMO LTDA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+56999000031; +56999000032</t>
+          <t>+56978374563; +56921741106</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1159,22 +1159,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>319069052</t>
+          <t>77918675K</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YV2XT4ZA1TA900112</t>
+          <t>YV2XT4ZA1TA276344</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A900112</t>
+          <t>A276344</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A900112 CONSTRUCTORA VALLE CENTRAL DEMO SPA</t>
+          <t>A276344 CONSTRUCTORA VALLE CENTRAL DEMO SPA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+56999000005; +56999000006</t>
+          <t>+56988939057; +56956368156</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1226,22 +1226,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>317643630</t>
+          <t>772902824</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YV2TE2AB8RA900095</t>
+          <t>YV2TE2AB8RA543380</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A900095</t>
+          <t>A543380</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A900095 CARGA MIXTA AUSTRAL DEMO SPA</t>
+          <t>A543380 CARGA MIXTA AUSTRAL DEMO SPA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+56999000013; +56999000014; +56999000015</t>
+          <t>+56924597160; +56981374654; +56986155157</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1293,22 +1293,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>32279098K</t>
+          <t>789555699</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YV2XT4ZA9PA900116</t>
+          <t>YV2XT4ZA9PA653268</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A900116</t>
+          <t>A653268</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A900116 SERVICIOS INDUSTRIALES BIOBIO DEMO SPA</t>
+          <t>A653268 SERVICIOS INDUSTRIALES BIOBIO DEMO SPA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+56999000010; +56999000011</t>
+          <t>+56946248600; +56959279643</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1360,22 +1360,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9BVRT4ZD6PE900038</t>
+          <t>9BVRT4ZD6PE891576</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E900038</t>
+          <t>E891576</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E900038 FORESTAL ARAUCANIA FICTICIA S.A.</t>
+          <t>E891576 FORESTAL ARAUCANIA FICTICIA S.A.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+56999000024; +56999000025; +56999000026</t>
+          <t>+56911363139; +56990241687; +56965985879</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1427,22 +1427,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>317802015</t>
+          <t>773747253</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YV2RT4ZA5RA900081</t>
+          <t>YV2RT4ZA5RA280482</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A900081</t>
+          <t>A280482</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A900081 TRANSPORTES JUAN PEREZ DEMO EIRL</t>
+          <t>A280482 TRANSPORTES JUAN PEREZ DEMO EIRL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1482,22 +1482,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9BVRT4ZC5TA900031</t>
+          <t>9BVRT4ZC5TA599724</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A900031</t>
+          <t>A599724</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A900031 FORESTAL ARAUCANIA FICTICIA S.A.</t>
+          <t>A599724 FORESTAL ARAUCANIA FICTICIA S.A.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+56999000024; +56999000025; +56999000026</t>
+          <t>+56911363139; +56990241687; +56965985879</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1549,22 +1549,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>321444752</t>
+          <t>785172752</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YV2XT4ZD6TE900125</t>
+          <t>YV2XT4ZD6TE839290</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>E900125</t>
+          <t>E839290</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E900125 LOGISTICA ATACAMA FICTICIA SPA</t>
+          <t>E839290 LOGISTICA ATACAMA FICTICIA SPA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+56999000007; +56999000008</t>
+          <t>+56964304013; +56975863067</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
